--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260810.xlsx
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>194,842,252</t>
+          <t>11,563,014</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>11,563,014</t>
+          <t>194,842,252</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>261,877,795</t>
+          <t>4,176,326</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4,176,326</t>
+          <t>261,877,795</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>17,799,662</t>
+          <t>1,873,362</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,873,362</t>
+          <t>2,032,785</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>2,032,785</t>
+          <t>17,799,662</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
